--- a/evaluation_results.xlsx
+++ b/evaluation_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -780,12 +780,470 @@
         <v>0.9200000000000002</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" t="n">
+        <v>300</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>26.94 ± 19.79</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>33.07 ± 19.78</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>0.9800000000000001</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>61.00 ± 32.95</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>28.96 ± 15.77</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>0.9800000000000001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Room Size</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Num Distractors</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Max Steps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Delta Theta</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Avg Steps LA-MAML</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Success Prob LA-MAML</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Avg Steps MAML</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Success Prob MAML</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Avg Steps Lang-Cond</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Success Prob Lang-Cond</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Avg Steps ANIL</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Success Prob ANIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" t="n">
+        <v>500</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>136.97 ± 36.32</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>236.86 ± 68.66</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>342.73 ± 98.62</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>0.4199999999999999</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>182.52 ± 28.79</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>0.8300000000000001</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3" t="n">
+        <v>500</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>212.81 ± 70.62</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>0.7400000000000001</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>288.78 ± 74.03</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>402.53 ± 60.35</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>244.14 ± 57.46</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="n">
+        <v>500</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>172.32 ± 41.83</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>0.8699999999999999</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>300.19 ± 75.19</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>342.59 ± 58.69</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>228.64 ± 70.13</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C5" t="n">
+        <v>500</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>259.31 ± 98.69</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0.5999999999999999</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>359.60 ± 72.30</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>364.28 ± 59.76</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>349.72 ± 61.52</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>0.4699999999999999</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" t="n">
+        <v>500</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>143.77 ± 42.37</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>244.09 ± 89.16</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>320.87 ± 62.59</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>207.93 ± 76.39</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>0.8000000000000002</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" t="n">
+        <v>500</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>240.74 ± 82.34</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>289.63 ± 89.33</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>377.35 ± 71.95</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>323.78 ± 65.54</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>0.5499999999999999</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" t="n">
+        <v>500</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>163.05 ± 35.01</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>0.8400000000000001</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>316.66 ± 64.87</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>363.82 ± 50.61</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>261.29 ± 67.79</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>0.6900000000000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -871,477 +1329,111 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>6</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
       </c>
       <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>300</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>28.46 ± 20.99</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>0.9800000000000001</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>51.53 ± 29.70</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>0.9800000000000001</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>74.95 ± 44.70</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>39.97 ± 30.76</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
         <v>2</v>
       </c>
-      <c r="C2" t="n">
-        <v>500</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>136.97 ± 36.32</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>236.86 ± 68.66</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>342.73 ± 98.62</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>0.4199999999999999</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>182.52 ± 28.79</t>
-        </is>
-      </c>
-      <c r="L2" t="n">
-        <v>0.8300000000000001</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>6</v>
-      </c>
-      <c r="B3" t="n">
-        <v>4</v>
-      </c>
       <c r="C3" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="D3" t="n">
         <v>0.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>212.81 ± 70.62</t>
+          <t>41.30 ± 22.95</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.7400000000000001</v>
+        <v>0.9700000000000001</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>288.78 ± 74.03</t>
+          <t>53.02 ± 29.14</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.51</v>
+        <v>0.9700000000000001</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>402.53 ± 60.35</t>
+          <t>72.67 ± 26.64</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0.28</v>
+        <v>0.96</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>244.14 ± 57.46</t>
+          <t>48.57 ± 34.44</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.74</v>
+        <v>0.9600000000000002</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>7</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
       </c>
       <c r="B4" t="n">
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>500</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>172.32 ± 41.83</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>0.8699999999999999</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>300.19 ± 75.19</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>342.59 ± 58.69</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>228.64 ± 70.13</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>0.78</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>7</v>
-      </c>
-      <c r="B5" t="n">
-        <v>5</v>
-      </c>
-      <c r="C5" t="n">
-        <v>500</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>259.31 ± 98.69</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>0.5999999999999999</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>359.60 ± 72.30</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>364.28 ± 59.76</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>349.72 ± 61.52</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
-        <v>0.4699999999999999</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B6" t="n">
-        <v>2</v>
-      </c>
-      <c r="C6" t="n">
-        <v>500</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>143.77 ± 42.37</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>244.09 ± 89.16</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>320.87 ± 62.59</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>207.93 ± 76.39</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>0.8000000000000002</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B7" t="n">
-        <v>4</v>
-      </c>
-      <c r="C7" t="n">
-        <v>500</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>240.74 ± 82.34</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>289.63 ± 89.33</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>377.35 ± 71.95</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>323.78 ± 65.54</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
-        <v>0.5499999999999999</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Room Size</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Num Distractors</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Max Steps</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Delta Theta</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Avg Steps LA-MAML</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Success Prob LA-MAML</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Avg Steps MAML</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Success Prob MAML</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Avg Steps Lang-Cond</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Success Prob Lang-Cond</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Avg Steps ANIL</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Success Prob ANIL</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>env</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="n">
-        <v>300</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>28.46 ± 20.99</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>0.9800000000000001</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>51.53 ± 29.70</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>0.9800000000000001</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>74.95 ± 44.70</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>39.97 ± 30.76</t>
-        </is>
-      </c>
-      <c r="L2" t="n">
-        <v>0.99</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>env</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C3" t="n">
-        <v>300</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>41.30 ± 22.95</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>0.9700000000000001</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>53.02 ± 29.14</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>0.9700000000000001</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>72.67 ± 26.64</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>48.57 ± 34.44</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>0.9600000000000002</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>env</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C4" t="n">
         <v>300</v>
       </c>
       <c r="D4" t="n">
@@ -1474,6 +1566,54 @@
       </c>
       <c r="L6" t="n">
         <v>0.89</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" t="n">
+        <v>300</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>57.53 ± 26.18</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>57.32 ± 31.30</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>87.74 ± 36.99</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>56.96 ± 42.12</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>0.93</v>
       </c>
     </row>
   </sheetData>

--- a/evaluation_results.xlsx
+++ b/evaluation_results.xlsx
@@ -2131,7 +2131,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2450,6 +2450,54 @@
         <v>0.34</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>800</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>133.05 ± 52.30</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>0.9700000000000001</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>636.73 ± 128.21</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>527.18 ± 66.31</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>560.68 ± 108.20</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2461,7 +2509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2780,6 +2828,54 @@
         <v>0.41</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>800</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>94.96 ± 56.66</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>502.69 ± 94.28</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>425.06 ± 110.98</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>520.99 ± 142.19</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2791,7 +2887,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3110,6 +3206,54 @@
         <v>0.72</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>env</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>252.29 ± 147.01</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>523.02 ± 264.85</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>548.55 ± 258.20</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0.6500000000000001</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>480.76 ± 248.18</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>0.73</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
